--- a/outputs/416-15.xlsx
+++ b/outputs/416-15.xlsx
@@ -20,9 +20,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/21/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/4/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/11/2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/27/2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/4/2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/18/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/1/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/20/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/25/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/2/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/21/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/26/2021</t>
   </si>
 </sst>
 </file>
@@ -134,20 +170,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -403,102 +447,102 @@
   <dimension ref="A1:A19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
-        <v>44307</v>
+      <c r="A2" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
-        <v>44320</v>
+      <c r="A3" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
-        <v>43780</v>
+      <c r="A4" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
-        <v>43888</v>
+      <c r="A5" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
-        <v>44047</v>
+      <c r="A6" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
-        <v>44214</v>
+      <c r="A7" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
-        <v>44214</v>
+      <c r="A8" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
-        <v>44228</v>
+      <c r="A9" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
-        <v>44216</v>
+      <c r="A10" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
-        <v>44221</v>
+      <c r="A11" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
-        <v>44216</v>
+      <c r="A12" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
-        <v>44221</v>
+      <c r="A13" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
-        <v>44229</v>
+      <c r="A14" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
-        <v>44217</v>
+      <c r="A15" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
-        <v>44222</v>
+      <c r="A16" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
-        <v>44222</v>
+      <c r="A17" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
-        <v>44217</v>
+      <c r="A18" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
-        <v>44217</v>
+      <c r="A19" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
